--- a/Libraries/Vehicle/Linkage/SpLA_S2LAR/sm_car_data_Linkage_SpLA_S2LAR.xlsx
+++ b/Libraries/Vehicle/Linkage/SpLA_S2LAR/sm_car_data_Linkage_SpLA_S2LAR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Linkage\SpLA_S2LAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EE708A-ECC3-4AD1-81BF-982E8E5189B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B763DF15-B1F0-4530-B2AC-ADC1C3D2CCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30390" yWindow="0" windowWidth="21600" windowHeight="15585" tabRatio="828" xr2:uid="{7F59BFDE-2DD5-4720-8334-1691F44FC63C}"/>
+    <workbookView xWindow="32685" yWindow="0" windowWidth="21600" windowHeight="15585" tabRatio="828" activeTab="1" xr2:uid="{7F59BFDE-2DD5-4720-8334-1691F44FC63C}"/>
   </bookViews>
   <sheets>
     <sheet name="S2LAR_Sedan_HambaLG_f" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="51">
   <si>
     <t>Units</t>
   </si>
@@ -1396,7 +1396,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="16" customWidth="1"/>
@@ -1408,7 +1408,7 @@
     <col min="11" max="11" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1428,7 +1428,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="J5" s="16"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="5" t="s">
         <v>13</v>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="J6" s="16"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="5" t="s">
         <v>12</v>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="J7" s="16"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="J8" s="16"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
         <v>13</v>
@@ -1569,174 +1569,187 @@
         <v>0.18855571428571433</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="5" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="23">
+        <v>-0.05</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.75</v>
+      </c>
+      <c r="H10" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6">
+      <c r="F11" s="12"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6">
         <f>5.80566/2</f>
         <v>2.9028299999999998</v>
       </c>
-      <c r="J10" s="16"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="J11" s="16"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0.18372714285714289</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0.63060000000000005</v>
-      </c>
-      <c r="H11" s="6">
-        <v>0.51255285714285714</v>
-      </c>
-      <c r="J11" s="16"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="F12" s="6">
-        <v>-0.16634428571428575</v>
+        <v>0.18372714285714289</v>
       </c>
       <c r="G12" s="6">
         <v>0.63060000000000005</v>
       </c>
       <c r="H12" s="6">
-        <v>0.53609214285714291</v>
+        <v>0.51255285714285714</v>
       </c>
       <c r="J12" s="16"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="6">
-        <v>4.8285714285714293E-2</v>
+        <v>-0.16634428571428575</v>
       </c>
       <c r="G13" s="6">
-        <v>0.89280000000000004</v>
+        <v>0.63060000000000005</v>
       </c>
       <c r="H13" s="6">
-        <v>0.54321428571428576</v>
+        <v>0.53609214285714291</v>
       </c>
       <c r="J13" s="16"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="F14" s="6">
+        <v>4.8285714285714293E-2</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0.89280000000000004</v>
+      </c>
       <c r="H14" s="6">
-        <v>5.4538000000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>0.54321428571428576</v>
+      </c>
+      <c r="J14" s="16"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
       <c r="B15" s="5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="6">
-        <v>-9.4157142857142894E-3</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0.89449999999999996</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
       <c r="H15" s="6">
-        <v>0.42648357142857141</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
+        <v>5.4538000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="B16" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" t="s">
         <v>12</v>
       </c>
       <c r="F16" s="6">
-        <v>0</v>
+        <v>-9.4157142857142894E-3</v>
       </c>
       <c r="G16" s="6">
-        <v>0.99209999999999998</v>
+        <v>0.89449999999999996</v>
       </c>
       <c r="H16" s="6">
-        <v>0.36214285714285716</v>
+        <v>0.42648357142857141</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="5" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="F17" s="6">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0.99209999999999998</v>
+      </c>
       <c r="H17" s="6">
-        <v>7.0371699999999997</v>
+        <v>0.36214285714285716</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="5" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6">
-        <v>0</v>
+        <v>7.0371699999999997</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" t="s">
@@ -1751,146 +1764,136 @@
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6">
-        <v>0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" t="s">
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>28</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6">
-        <v>1.76</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>11</v>
+      <c r="A23" s="4"/>
+      <c r="B23" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" s="22">
-        <v>0.13</v>
-      </c>
-      <c r="G23" s="22">
-        <v>0.65</v>
-      </c>
-      <c r="H23" s="22">
-        <v>0.24</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>46</v>
+        <v>14</v>
+      </c>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6">
+        <v>1.76</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5" t="s">
-        <v>13</v>
+      <c r="A24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>11</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="6">
+      <c r="E24" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="22">
         <v>0.13</v>
       </c>
-      <c r="G24" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="H24" s="6">
-        <v>0.23</v>
+      <c r="G24" s="22">
+        <v>0.65</v>
+      </c>
+      <c r="H24" s="22">
+        <v>0.24</v>
+      </c>
+      <c r="J24" s="18" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0.13</v>
+      </c>
+      <c r="G25" s="6">
+        <v>0.91</v>
+      </c>
       <c r="H25" s="6">
-        <v>5.2778799999999997</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>32</v>
+      <c r="A26" s="4"/>
+      <c r="B26" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" t="s">
-        <v>47</v>
-      </c>
-      <c r="F26" s="20">
-        <v>2.6557142857142869E-3</v>
-      </c>
-      <c r="G26" s="21">
-        <v>0.62</v>
-      </c>
-      <c r="H26" s="21">
-        <v>0.65</v>
-      </c>
-      <c r="J26" s="13" t="s">
-        <v>47</v>
+        <v>14</v>
+      </c>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6">
+        <v>5.2778799999999997</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
+      <c r="A27" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="B27" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" t="s">
@@ -1900,13 +1903,13 @@
         <v>47</v>
       </c>
       <c r="F27" s="20">
-        <v>-5.5166428571428582E-2</v>
+        <v>2.6557142857142869E-3</v>
       </c>
       <c r="G27" s="21">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="H27" s="21">
-        <v>0.19</v>
+        <v>0.65</v>
       </c>
       <c r="J27" s="13" t="s">
         <v>47</v>
@@ -1914,23 +1917,33 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
-      <c r="B28" s="5" t="s">
-        <v>34</v>
+      <c r="B28" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6">
-        <v>3.6529410000000002</v>
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28" s="20">
+        <v>-5.5166428571428582E-2</v>
+      </c>
+      <c r="G28" s="21">
+        <v>0.85</v>
+      </c>
+      <c r="H28" s="21">
+        <v>0.19</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" t="s">
@@ -1939,36 +1952,30 @@
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6">
-        <v>4.3157700000000006</v>
+        <v>3.6529410000000002</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>37</v>
+      <c r="A30" s="4"/>
+      <c r="B30" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" t="s">
-        <v>48</v>
-      </c>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="19">
-        <v>0.1</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>48</v>
+        <v>14</v>
+      </c>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6">
+        <v>4.3157700000000006</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
+      <c r="A31" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="B31" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" t="s">
@@ -1980,47 +1987,52 @@
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
       <c r="H31" s="19">
-        <v>-0.15</v>
+        <v>0.1</v>
       </c>
       <c r="J31" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="15" t="s">
-        <v>40</v>
+      <c r="A32" s="4"/>
+      <c r="B32" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="19">
+        <v>-0.15</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
-      <c r="E33" s="8"/>
+      <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
       <c r="H33" s="15" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>8</v>
@@ -2034,28 +2046,44 @@
         <v>44</v>
       </c>
     </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A26">
+  <conditionalFormatting sqref="A27">
     <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A32:A34">
+  <conditionalFormatting sqref="A33:A35">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26:B31">
+  <conditionalFormatting sqref="A27:B32">
     <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E26:E31">
+  <conditionalFormatting sqref="E27:E32">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J30:J31">
+  <conditionalFormatting sqref="J31:J32">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
